--- a/历史提交归档/260424完备-带指示LED/完备资源分配0424.xlsx
+++ b/历史提交归档/260424完备-带指示LED/完备资源分配0424.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
+    <workbookView minimized="1" xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="102">
   <si>
     <t>MT6701-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -394,6 +394,10 @@
   </si>
   <si>
     <t>稳定状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -840,17 +844,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F41"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="22.26953125" customWidth="1"/>
-    <col min="2" max="2" width="25.6328125" customWidth="1"/>
-    <col min="3" max="3" width="21.7265625" customWidth="1"/>
-    <col min="4" max="4" width="22.81640625" customWidth="1"/>
-    <col min="5" max="5" width="17.81640625" customWidth="1"/>
-    <col min="6" max="6" width="18.7265625" customWidth="1"/>
+    <col min="1" max="1" width="22.25" customWidth="1"/>
+    <col min="2" max="2" width="25.625" customWidth="1"/>
+    <col min="3" max="3" width="21.75" customWidth="1"/>
+    <col min="4" max="4" width="22.875" customWidth="1"/>
+    <col min="5" max="5" width="17.875" customWidth="1"/>
+    <col min="6" max="6" width="18.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -870,7 +874,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -890,7 +894,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -910,7 +914,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -930,7 +934,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
@@ -950,7 +954,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
@@ -968,7 +972,7 @@
       </c>
       <c r="F6" s="2"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>3</v>
       </c>
@@ -982,7 +986,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
         <v>0</v>
       </c>
@@ -996,7 +1000,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
         <v>1</v>
       </c>
@@ -1010,7 +1014,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
         <v>2</v>
       </c>
@@ -1024,7 +1028,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
         <v>34</v>
       </c>
@@ -1038,7 +1042,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
         <v>35</v>
       </c>
@@ -1052,7 +1056,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
         <v>36</v>
       </c>
@@ -1066,17 +1070,17 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="9" t="s">
         <v>0</v>
       </c>
@@ -1093,7 +1097,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="9" t="s">
         <v>1</v>
       </c>
@@ -1107,7 +1111,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" s="9" t="s">
         <v>2</v>
       </c>
@@ -1121,21 +1125,24 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A22" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E22" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23" s="8" t="s">
         <v>74</v>
       </c>
@@ -1149,7 +1156,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A24" s="8" t="s">
         <v>75</v>
       </c>
@@ -1163,7 +1170,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A25" s="9" t="s">
         <v>94</v>
       </c>
@@ -1177,17 +1184,17 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" s="9" t="s">
         <v>42</v>
       </c>
@@ -1201,7 +1208,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" s="10" t="s">
         <v>46</v>
       </c>
@@ -1218,7 +1225,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A30" s="9" t="s">
         <v>50</v>
       </c>
@@ -1232,7 +1239,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A31" s="9" t="s">
         <v>53</v>
       </c>
@@ -1246,7 +1253,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
         <v>86</v>
       </c>
@@ -1254,7 +1261,7 @@
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
         <v>87</v>
       </c>
@@ -1268,7 +1275,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
         <v>88</v>
       </c>
@@ -1280,7 +1287,7 @@
       </c>
       <c r="D35" s="8"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
         <v>89</v>
       </c>
@@ -1292,7 +1299,7 @@
       </c>
       <c r="D36" s="8"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A37" s="8" t="s">
         <v>90</v>
       </c>
@@ -1304,7 +1311,7 @@
       </c>
       <c r="D37" s="8"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A38" s="8" t="s">
         <v>91</v>
       </c>
@@ -1316,7 +1323,7 @@
       </c>
       <c r="D38" s="8"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A39" s="8" t="s">
         <v>98</v>
       </c>
@@ -1328,7 +1335,7 @@
       </c>
       <c r="D39" s="8"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A40" s="8" t="s">
         <v>99</v>
       </c>
@@ -1340,7 +1347,7 @@
       </c>
       <c r="D40" s="8"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A41" s="8" t="s">
         <v>100</v>
       </c>
